--- a/data/trans_camb/P71_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,22</t>
+          <t>6,47; 14,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 22,06</t>
+          <t>12,63; 22,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,79</t>
+          <t>-8,29; 1,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 0,16</t>
+          <t>-7,67; -0,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 13,67</t>
+          <t>5,12; 14,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,91; -9,08</t>
+          <t>-16,76; -9,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,38</t>
+          <t>-0,4; 5,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 16,37</t>
+          <t>9,91; 16,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -5,6</t>
+          <t>-11,59; -5,83</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,58; 55,12</t>
+          <t>20,14; 54,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,73; 80,51</t>
+          <t>39,57; 80,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 6,71</t>
+          <t>-25,57; 4,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 0,16</t>
+          <t>-18,3; -0,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 35,79</t>
+          <t>12,34; 36,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,17; -23,55</t>
+          <t>-40,26; -24,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 15,55</t>
+          <t>-1,08; 16,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,6; 47,58</t>
+          <t>26,71; 47,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,39; -16,29</t>
+          <t>-31,36; -16,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,89; 18,28</t>
+          <t>12,77; 18,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 22,79</t>
+          <t>16,8; 22,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,33</t>
+          <t>-7,45; -0,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 13,41</t>
+          <t>7,02; 12,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 15,26</t>
+          <t>9,55; 15,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 3,22</t>
+          <t>-10,3; 3,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 14,71</t>
+          <t>10,84; 15,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,18</t>
+          <t>13,76; 18,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,28</t>
+          <t>-7,35; 0,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,65; 137,08</t>
+          <t>79,42; 138,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>107,09; 170,29</t>
+          <t>104,75; 168,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -2,68</t>
+          <t>-46,71; -2,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,42; 63,99</t>
+          <t>29,09; 61,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,01; 74,23</t>
+          <t>40,34; 74,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 15,12</t>
+          <t>-43,95; 17,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,51; 85,13</t>
+          <t>55,18; 87,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 104,92</t>
+          <t>71,65; 104,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 1,79</t>
+          <t>-38,12; 3,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,42</t>
+          <t>1,77; 9,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,55</t>
+          <t>0,59; 7,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; -1,7</t>
+          <t>-6,73; -1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,41</t>
+          <t>-2,06; 7,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,34</t>
+          <t>-2,44; 6,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -3,53</t>
+          <t>-10,51; -3,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,34</t>
+          <t>1,07; 7,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,04</t>
+          <t>0,37; 6,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -3,15</t>
+          <t>-7,44; -3,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,67; 179,83</t>
+          <t>17,16; 165,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 140,87</t>
+          <t>4,45; 136,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,71; -26,05</t>
+          <t>-79,28; -26,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 77,08</t>
+          <t>-15,71; 78,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 62,91</t>
+          <t>-17,3; 67,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,77; -33,86</t>
+          <t>-69,93; -33,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,17; 92,27</t>
+          <t>8,81; 88,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 74,34</t>
+          <t>3,03; 77,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,82; -38,92</t>
+          <t>-69,52; -39,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 14,66</t>
+          <t>10,56; 14,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,05; 17,47</t>
+          <t>13,1; 17,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -3,81</t>
+          <t>-9,31; -4,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,96</t>
+          <t>1,46; 6,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,34</t>
+          <t>5,43; 10,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -4,69</t>
+          <t>-14,13; -5,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,62</t>
+          <t>6,63; 9,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,13</t>
+          <t>10,15; 13,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -5,24</t>
+          <t>-10,62; -5,5</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>54,16; 85,27</t>
+          <t>54,23; 86,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,56; 101,75</t>
+          <t>68,47; 102,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,49; -22,25</t>
+          <t>-50,13; -23,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 22,69</t>
+          <t>4,9; 22,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 38,47</t>
+          <t>18,92; 37,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,18; -16,86</t>
+          <t>-49,23; -19,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,95; 43,18</t>
+          <t>27,93; 43,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>41,37; 58,98</t>
+          <t>43,03; 59,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,89; -23,05</t>
+          <t>-45,19; -24,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P71_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,82</t>
+          <t>-12,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,55</t>
+          <t>-7,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 14,95</t>
+          <t>6,6; 15,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 22,22</t>
+          <t>12,46; 21,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,4</t>
+          <t>-5,7; 3,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,15</t>
+          <t>-7,42; 0,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 14,06</t>
+          <t>5,6; 13,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,76; -9,26</t>
+          <t>-15,9; -8,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,44</t>
+          <t>-0,44; 5,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,91; 16,34</t>
+          <t>9,96; 16,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -5,83</t>
+          <t>-9,85; -4,23</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,55%</t>
+          <t>-3,69%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-31,98%</t>
+          <t>-30,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-23,99%</t>
+          <t>-20,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,14; 54,88</t>
+          <t>20,72; 55,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,57; 80,88</t>
+          <t>39,21; 78,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 4,85</t>
+          <t>-17,81; 11,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,3; -0,47</t>
+          <t>-17,72; 1,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 36,8</t>
+          <t>13,26; 35,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,26; -24,15</t>
+          <t>-37,75; -22,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 16,09</t>
+          <t>-1,12; 15,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,71; 47,16</t>
+          <t>26,71; 47,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,36; -16,8</t>
+          <t>-26,98; -12,41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,57</t>
+          <t>-6,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>-3,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,18</t>
+          <t>13,18; 18,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,8; 22,37</t>
+          <t>16,91; 22,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -0,38</t>
+          <t>-2,72; 2,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 12,86</t>
+          <t>6,87; 13,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 15,63</t>
+          <t>9,22; 15,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 3,73</t>
+          <t>-8,45; -3,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 15,07</t>
+          <t>10,89; 14,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 18,07</t>
+          <t>13,87; 18,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,49</t>
+          <t>-4,9; -1,22</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,47%</t>
+          <t>-2,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-24,76%</t>
+          <t>-26,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,72%</t>
+          <t>-16,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,42; 138,39</t>
+          <t>82,64; 140,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>104,75; 168,28</t>
+          <t>104,45; 171,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -2,59</t>
+          <t>-17,66; 15,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 61,84</t>
+          <t>28,22; 63,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,34; 74,82</t>
+          <t>38,2; 75,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 17,16</t>
+          <t>-34,97; -15,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,18; 87,05</t>
+          <t>56,09; 86,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,65; 104,84</t>
+          <t>71,24; 104,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 3,06</t>
+          <t>-25,27; -7,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,23</t>
+          <t>-3,74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,83</t>
+          <t>-6,27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-4,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,11</t>
+          <t>1,54; 9,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,61</t>
+          <t>0,4; 7,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -1,59</t>
+          <t>-6,51; -1,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,75</t>
+          <t>-1,89; 6,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,62</t>
+          <t>-2,63; 5,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -3,55</t>
+          <t>-9,75; -2,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,33</t>
+          <t>1,33; 7,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,05</t>
+          <t>0,44; 5,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -3,21</t>
+          <t>-7,01; -2,59</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-61,33%</t>
+          <t>-54,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-56,8%</t>
+          <t>-52,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-57,49%</t>
+          <t>-51,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,16; 165,08</t>
+          <t>16,92; 174,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 136,9</t>
+          <t>3,03; 143,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,28; -26,66</t>
+          <t>-75,13; -16,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 78,2</t>
+          <t>-15,2; 67,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 67,76</t>
+          <t>-18,65; 60,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,93; -33,17</t>
+          <t>-67,52; -27,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,81; 88,69</t>
+          <t>12,43; 92,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 77,37</t>
+          <t>3,82; 71,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,52; -39,56</t>
+          <t>-64,82; -31,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,89</t>
+          <t>-10,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,41</t>
+          <t>-7,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,83</t>
+          <t>10,39; 14,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,1; 17,53</t>
+          <t>13,15; 17,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -4,12</t>
+          <t>-5,77; -1,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,16</t>
+          <t>1,6; 6,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,13</t>
+          <t>5,62; 10,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -5,65</t>
+          <t>-12,89; -9,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,71</t>
+          <t>6,44; 9,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,13</t>
+          <t>9,91; 13,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -5,5</t>
+          <t>-8,81; -5,91</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-32,78%</t>
+          <t>-20,57%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,13%</t>
+          <t>-39,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-36,54%</t>
+          <t>-31,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>54,23; 86,5</t>
+          <t>54,82; 85,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68,47; 102,39</t>
+          <t>68,48; 104,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,13; -23,65</t>
+          <t>-30,14; -11,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,9; 22,83</t>
+          <t>5,59; 22,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,92; 37,76</t>
+          <t>19,36; 38,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,23; -19,38</t>
+          <t>-44,12; -33,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,93; 43,86</t>
+          <t>26,97; 43,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,03; 59,3</t>
+          <t>41,97; 59,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -24,51</t>
+          <t>-36,92; -26,77</t>
         </is>
       </c>
     </row>
